--- a/apps/api/assets/vocabulary/初中/外研版/外研版初中英语八年级下册.xlsx
+++ b/apps/api/assets/vocabulary/初中/外研版/外研版初中英语八年级下册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D269"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -691,6 +691,16 @@
           <t>have a try</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 试一试
@@ -753,6 +763,16 @@
           <t>sweet tooth</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. (指人)爱吃甜食的
@@ -1027,6 +1047,16 @@
           <t>be proud of ...</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 以…自豪
@@ -1087,6 +1117,16 @@
           <t>sb. can't wait</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 等不及；迫不及待；不能等了</t>
@@ -1120,6 +1160,16 @@
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>at school</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1304,6 +1354,16 @@
           <t>first prize</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 头奖
@@ -1365,6 +1425,16 @@
           <t>write about</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 写…的事, 写到…, 把（某事）作为写作的主题</t>
@@ -1735,6 +1805,16 @@
           <t>count down</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (9,8,7,… 0 地)倒数；(火箭发射时)倒数秒数
@@ -1987,6 +2067,16 @@
           <t>no problem</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 没问题
@@ -2092,6 +2182,16 @@
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>space travel</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -2224,6 +2324,16 @@
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>solar system</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -2672,6 +2782,16 @@
           <t>catch a cold</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 【医】感冒
@@ -2709,6 +2829,16 @@
           <t>take sb.'s temperature</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -2719,6 +2849,16 @@
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>fast food</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -2901,6 +3041,16 @@
           <t>take part in sth.</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 参加；贡献
@@ -2935,6 +3085,16 @@
       <c r="A112" s="2" t="inlineStr">
         <is>
           <t>in excellent condition</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -3111,6 +3271,16 @@
           <t>feel awful</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 感觉难受；感觉很糟糕；感到痛苦的</t>
@@ -3121,6 +3291,16 @@
       <c r="A121" s="2" t="inlineStr">
         <is>
           <t>all over</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -3348,6 +3528,16 @@
           <t>can't help doing sth.</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 禁不住做某事；情不自禁做某事；忍不住做某事</t>
@@ -3407,6 +3597,16 @@
           <t>orange-and-white</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 橘白相间的</t>
@@ -3439,6 +3639,16 @@
       <c r="A136" s="2" t="inlineStr">
         <is>
           <t>win the heart of sb.</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -3853,6 +4063,16 @@
           <t>tidy up</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 整理干净
@@ -3886,6 +4106,16 @@
       <c r="A156" s="2" t="inlineStr">
         <is>
           <t>have a look</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -4253,6 +4483,16 @@
           <t>come out</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 出来
@@ -4287,6 +4527,16 @@
       <c r="A174" s="2" t="inlineStr">
         <is>
           <t>as a result</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -4373,6 +4623,16 @@
           <t>make a list</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 在名册中
@@ -4406,6 +4666,16 @@
       <c r="A180" s="2" t="inlineStr">
         <is>
           <t>at the end of ...</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -4627,6 +4897,16 @@
       <c r="A190" s="2" t="inlineStr">
         <is>
           <t>at the same time</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -4691,6 +4971,16 @@
           <t>depend on</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 依靠
@@ -4802,6 +5092,16 @@
           <t>daily life</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 起居
@@ -4886,6 +5186,16 @@
           <t>stay in touch with sb.</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 与……保持联系；与……保持联络；和……保持联系</t>
@@ -4970,6 +5280,16 @@
           <t>fill out</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 填写(表格等)；变胖；长胖；胖起来
@@ -5028,6 +5348,16 @@
           <t>point out</t>
         </is>
       </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 指出
@@ -5084,6 +5414,16 @@
       <c r="A212" s="2" t="inlineStr">
         <is>
           <t>at the top of ...</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -5246,6 +5586,16 @@
           <t>wake sb. up</t>
         </is>
       </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 同“wake”；叫醒；醒来；振作起来
@@ -5681,6 +6031,16 @@
           <t>join in</t>
         </is>
       </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 参加；参与
@@ -5692,6 +6052,16 @@
       <c r="A239" s="2" t="inlineStr">
         <is>
           <t>no problem</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -5731,6 +6101,16 @@
           <t>in silence</t>
         </is>
       </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 沉默着
@@ -5818,6 +6198,16 @@
           <t>day by day</t>
         </is>
       </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. “day after day”的变体
@@ -6043,6 +6433,16 @@
           <t>show sb. around</t>
         </is>
       </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 带…参观
@@ -6054,6 +6454,16 @@
       <c r="A256" s="2" t="inlineStr">
         <is>
           <t>on air</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -6250,6 +6660,16 @@
       <c r="A265" s="2" t="inlineStr">
         <is>
           <t>in person</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
